--- a/data/prod_parameters/LayerHerd.xlsx
+++ b/data/prod_parameters/LayerHerd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="2" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="118">
   <si>
     <t>value</t>
   </si>
@@ -416,9 +416,6 @@
   </si>
   <si>
     <t>share_in_ration</t>
-  </si>
-  <si>
-    <t>Only farm A now… use mean?</t>
   </si>
 </sst>
 </file>
@@ -427,7 +424,7 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="2">
     <numFmt numFmtId="164" formatCode="0.0"/>
-    <numFmt numFmtId="167" formatCode="0.000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
   </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
@@ -686,7 +683,7 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -781,15 +778,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -800,6 +788,15 @@
     <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1498,7 +1495,7 @@
         <v>14</v>
       </c>
       <c r="E27" s="8">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F27" t="s">
         <v>15</v>
@@ -1515,11 +1512,11 @@
       <c r="C29" s="6"/>
       <c r="D29" s="6"/>
       <c r="E29" s="6"/>
-      <c r="F29" s="74" t="s">
+      <c r="F29" s="71" t="s">
         <v>112</v>
       </c>
       <c r="G29" s="6"/>
-      <c r="H29" s="74" t="s">
+      <c r="H29" s="71" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1550,7 +1547,7 @@
       </c>
       <c r="E31" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B31,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>31.390907416054425</v>
+        <v>35.955136032867976</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1565,7 +1562,7 @@
       </c>
       <c r="E32" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B32,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>37.754740931981566</v>
+        <v>31.729574287646834</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1681,11 +1678,11 @@
       <c r="C42" s="6"/>
       <c r="D42" s="6"/>
       <c r="E42" s="6"/>
-      <c r="F42" s="74" t="s">
+      <c r="F42" s="71" t="s">
         <v>114</v>
       </c>
       <c r="G42" s="6"/>
-      <c r="H42" s="74" t="s">
+      <c r="H42" s="71" t="s">
         <v>115</v>
       </c>
     </row>
@@ -1938,7 +1935,7 @@
       </c>
       <c r="E56" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C56,'Feed rations'!$V$5:$V$17,0),MATCH(B56,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>43.682112995233247</v>
+        <v>52.05847593594973</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1956,7 +1953,7 @@
       </c>
       <c r="E57" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C57,'Feed rations'!$V$5:$V$17,0),MATCH(B57,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.6881300304758931</v>
+        <v>1.3440650152379465</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1974,7 +1971,7 @@
       </c>
       <c r="E58" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C58,'Feed rations'!$V$5:$V$17,0),MATCH(B58,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>16.800812690474331</v>
+        <v>12.963626223585813</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1992,7 +1989,7 @@
       </c>
       <c r="E59" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C59,'Feed rations'!$V$5:$V$17,0),MATCH(B59,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>3.920189627777344</v>
+        <v>1.960094813888672</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2046,7 +2043,7 @@
       </c>
       <c r="E62" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C62,'Feed rations'!$V$5:$V$17,0),MATCH(B62,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>27.048006043083014</v>
+        <v>24.343208405260931</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2082,7 +2079,7 @@
       </c>
       <c r="E64" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C64,'Feed rations'!$V$5:$V$17,0),MATCH(B64,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.7471204866054095</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2118,7 +2115,7 @@
       </c>
       <c r="E66" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C66,'Feed rations'!$V$5:$V$17,0),MATCH(B66,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.8607486129561623</v>
+        <v>5.5834091194714803</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2172,7 +2169,7 @@
       </c>
       <c r="E69" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C69,'Feed rations'!$V$5:$V$17,0),MATCH(B69,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>39.526806465933717</v>
+        <v>55.910178622144024</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2190,7 +2187,7 @@
       </c>
       <c r="E70" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C70,'Feed rations'!$V$5:$V$17,0),MATCH(B70,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.6950095317682083</v>
+        <v>1.3475047658841042</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2208,7 +2205,7 @@
       </c>
       <c r="E71" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C71,'Feed rations'!$V$5:$V$17,0),MATCH(B71,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.089650850024807</v>
+        <v>9.5448254250124034</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2226,7 +2223,7 @@
       </c>
       <c r="E72" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C72,'Feed rations'!$V$5:$V$17,0),MATCH(B72,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>6.4006476379494952</v>
+        <v>3.2003238189747476</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2280,7 +2277,7 @@
       </c>
       <c r="E75" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C75,'Feed rations'!$V$5:$V$17,0),MATCH(B75,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>23.785025983861281</v>
+        <v>21.742772443376154</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2316,7 +2313,7 @@
       </c>
       <c r="E77" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C77,'Feed rations'!$V$5:$V$17,0),MATCH(B77,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2334,7 +2331,7 @@
       </c>
       <c r="E78" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C78,'Feed rations'!$V$5:$V$17,0),MATCH(B78,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.7576841720418876</v>
+        <v>1.3788420860209438</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2352,7 +2349,7 @@
       </c>
       <c r="E79" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C79,'Feed rations'!$V$5:$V$17,0),MATCH(B79,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.7451753584205987</v>
+        <v>5.5412311187951762</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2406,7 +2403,7 @@
       </c>
       <c r="E82" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C82,'Feed rations'!$V$5:$V$17,0),MATCH(B82,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>45.302303640223286</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2424,7 +2421,7 @@
       </c>
       <c r="E83" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C83,'Feed rations'!$V$5:$V$17,0),MATCH(B83,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.7046151426998981</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2442,7 +2439,7 @@
       </c>
       <c r="E84" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C84,'Feed rations'!$V$5:$V$17,0),MATCH(B84,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>16.903844641874365</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2460,7 +2457,7 @@
       </c>
       <c r="E85" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C85,'Feed rations'!$V$5:$V$17,0),MATCH(B85,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>4.3949996068873345</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2514,7 +2511,7 @@
       </c>
       <c r="E88" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C88,'Feed rations'!$V$5:$V$17,0),MATCH(B88,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.949157428519012</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2550,7 +2547,7 @@
       </c>
       <c r="E90" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C90,'Feed rations'!$V$5:$V$17,0),MATCH(B90,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2568,7 +2565,7 @@
       </c>
       <c r="E91" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C91,'Feed rations'!$V$5:$V$17,0),MATCH(B91,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.7656524359881551</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2586,7 +2583,7 @@
       </c>
       <c r="E92" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C92,'Feed rations'!$V$5:$V$17,0),MATCH(B92,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>4.9794271038079518</v>
+        <v>5.1583569914888532</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2640,7 +2637,7 @@
       </c>
       <c r="E95" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C95,'Feed rations'!$V$5:$V$17,0),MATCH(B95,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>45.302303640223286</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2658,7 +2655,7 @@
       </c>
       <c r="E96" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C96,'Feed rations'!$V$5:$V$17,0),MATCH(B96,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.7046151426998981</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2676,7 +2673,7 @@
       </c>
       <c r="E97" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C97,'Feed rations'!$V$5:$V$17,0),MATCH(B97,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>16.903844641874365</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2694,7 +2691,7 @@
       </c>
       <c r="E98" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C98,'Feed rations'!$V$5:$V$17,0),MATCH(B98,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>4.3949996068873345</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2748,7 +2745,7 @@
       </c>
       <c r="E101" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C101,'Feed rations'!$V$5:$V$17,0),MATCH(B101,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.949157428519012</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2784,7 +2781,7 @@
       </c>
       <c r="E103" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C103,'Feed rations'!$V$5:$V$17,0),MATCH(B103,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2802,7 +2799,7 @@
       </c>
       <c r="E104" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C104,'Feed rations'!$V$5:$V$17,0),MATCH(B104,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.7656524359881551</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2820,7 +2817,7 @@
       </c>
       <c r="E105" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C105,'Feed rations'!$V$5:$V$17,0),MATCH(B105,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>4.9794271038079518</v>
+        <v>5.1583569914888532</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -4158,7 +4155,7 @@
       <c r="X3" s="54"/>
       <c r="Y3" s="54"/>
       <c r="Z3" s="54"/>
-      <c r="AA3" s="71"/>
+      <c r="AA3" s="68"/>
       <c r="AB3" s="63" t="s">
         <v>42</v>
       </c>
@@ -4234,19 +4231,19 @@
       <c r="V4" s="23" t="s">
         <v>93</v>
       </c>
-      <c r="W4" s="68" t="s">
+      <c r="W4" s="76" t="s">
         <v>47</v>
       </c>
-      <c r="X4" s="69" t="s">
+      <c r="X4" s="77" t="s">
         <v>48</v>
       </c>
-      <c r="Y4" s="69" t="s">
+      <c r="Y4" s="77" t="s">
         <v>49</v>
       </c>
-      <c r="Z4" s="69" t="s">
+      <c r="Z4" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="AA4" s="70" t="s">
+      <c r="AA4" s="78" t="s">
         <v>94</v>
       </c>
       <c r="AB4" s="65" t="s">
@@ -4297,31 +4294,31 @@
         <v>49</v>
       </c>
       <c r="N5" s="39">
-        <f>F5*$D5/F$25</f>
+        <f t="shared" ref="N5:T5" si="3">F5*$D5/F$25</f>
         <v>43.682112995233247</v>
       </c>
       <c r="O5" s="40">
-        <f>G5*$D5/G$25</f>
+        <f t="shared" si="3"/>
         <v>39.526806465933717</v>
       </c>
       <c r="P5" s="40">
-        <f>H5*$D5/H$25</f>
+        <f t="shared" si="3"/>
         <v>45.302303640223286</v>
       </c>
       <c r="Q5" s="40">
-        <f>I5*$D5/I$25</f>
+        <f t="shared" si="3"/>
         <v>60.43483887666622</v>
       </c>
       <c r="R5" s="40">
-        <f>J5*$D5/J$25</f>
+        <f t="shared" si="3"/>
         <v>72.29355077835433</v>
       </c>
       <c r="S5" s="39">
-        <f>K5*$D5/K$25</f>
+        <f t="shared" si="3"/>
         <v>58.016195973989106</v>
       </c>
       <c r="T5" s="41">
-        <f>L5*$D5/L$25</f>
+        <f t="shared" si="3"/>
         <v>57.595845007858948</v>
       </c>
       <c r="U5" s="4"/>
@@ -4334,22 +4331,22 @@
         <v>43.682112995233247</v>
       </c>
       <c r="X5" s="40">
-        <f>N5</f>
-        <v>43.682112995233247</v>
+        <f>(N5+Q5)/2</f>
+        <v>52.05847593594973</v>
       </c>
       <c r="Y5" s="40">
-        <f t="shared" ref="Y5:Z12" si="3">O5</f>
-        <v>39.526806465933717</v>
+        <f>(O5+R5)/2</f>
+        <v>55.910178622144024</v>
       </c>
       <c r="Z5" s="40">
-        <f t="shared" si="3"/>
-        <v>45.302303640223286</v>
-      </c>
-      <c r="AA5" s="75">
+        <f>(P5+R5)/2</f>
+        <v>58.797927209288808</v>
+      </c>
+      <c r="AA5" s="72">
         <f>Z5</f>
-        <v>45.302303640223286</v>
-      </c>
-      <c r="AB5" s="39">
+        <v>58.797927209288808</v>
+      </c>
+      <c r="AB5" s="40">
         <f>W5</f>
         <v>43.682112995233247</v>
       </c>
@@ -4365,7 +4362,7 @@
         <f>T5</f>
         <v>57.595845007858948</v>
       </c>
-      <c r="AF5" s="75">
+      <c r="AF5" s="72">
         <f>AE5</f>
         <v>57.595845007858948</v>
       </c>
@@ -4394,76 +4391,76 @@
       <c r="K6" s="27"/>
       <c r="L6" s="29"/>
       <c r="N6" s="42">
-        <f t="shared" ref="N6:N22" si="4">F6*$D6/F$25</f>
+        <f t="shared" ref="N6:N18" si="4">F6*$D6/F$25</f>
         <v>2.6881300304758931</v>
       </c>
       <c r="O6" s="43">
-        <f t="shared" ref="O6:O22" si="5">G6*$D6/G$25</f>
+        <f t="shared" ref="O6:O18" si="5">G6*$D6/G$25</f>
         <v>2.6950095317682083</v>
       </c>
       <c r="P6" s="43">
-        <f t="shared" ref="P6:P22" si="6">H6*$D6/H$25</f>
+        <f t="shared" ref="P6:P18" si="6">H6*$D6/H$25</f>
         <v>2.7046151426998981</v>
       </c>
       <c r="Q6" s="43">
-        <f t="shared" ref="Q6:Q22" si="7">I6*$D6/I$25</f>
+        <f t="shared" ref="Q6:Q18" si="7">I6*$D6/I$25</f>
         <v>0</v>
       </c>
       <c r="R6" s="43">
-        <f t="shared" ref="R6:R22" si="8">J6*$D6/J$25</f>
+        <f t="shared" ref="R6:R18" si="8">J6*$D6/J$25</f>
         <v>0</v>
       </c>
       <c r="S6" s="42">
-        <f t="shared" ref="S6:S22" si="9">K6*$D6/K$25</f>
+        <f t="shared" ref="S6:S18" si="9">K6*$D6/K$25</f>
         <v>0</v>
       </c>
       <c r="T6" s="44">
-        <f t="shared" ref="T6:T22" si="10">L6*$D6/L$25</f>
+        <f t="shared" ref="T6:T18" si="10">L6*$D6/L$25</f>
         <v>0</v>
       </c>
       <c r="U6" s="4"/>
       <c r="V6" s="4" t="str">
-        <f t="shared" ref="V6:V20" si="11">B6</f>
+        <f t="shared" ref="V6:V13" si="11">B6</f>
         <v>maize</v>
       </c>
       <c r="W6" s="42">
-        <f t="shared" ref="W6:W17" si="12">N6</f>
+        <f t="shared" ref="W6:W12" si="12">N6</f>
         <v>2.6881300304758931</v>
       </c>
       <c r="X6" s="43">
-        <f t="shared" ref="X6:X17" si="13">N6</f>
+        <f t="shared" ref="X6:X12" si="13">(N6+Q6)/2</f>
+        <v>1.3440650152379465</v>
+      </c>
+      <c r="Y6" s="43">
+        <f t="shared" ref="Y6:Y12" si="14">(O6+R6)/2</f>
+        <v>1.3475047658841042</v>
+      </c>
+      <c r="Z6" s="43">
+        <f t="shared" ref="Z6:Z12" si="15">(P6+R6)/2</f>
+        <v>1.3523075713499491</v>
+      </c>
+      <c r="AA6" s="73">
+        <f t="shared" ref="AA6:AA13" si="16">Z6</f>
+        <v>1.3523075713499491</v>
+      </c>
+      <c r="AB6" s="43">
+        <f t="shared" ref="AB6:AB17" si="17">W6</f>
         <v>2.6881300304758931</v>
       </c>
-      <c r="Y6" s="43">
-        <f t="shared" si="3"/>
-        <v>2.6950095317682083</v>
-      </c>
-      <c r="Z6" s="43">
-        <f t="shared" si="3"/>
-        <v>2.7046151426998981</v>
-      </c>
-      <c r="AA6" s="76">
-        <f t="shared" ref="AA6:AA18" si="14">Z6</f>
-        <v>2.7046151426998981</v>
-      </c>
-      <c r="AB6" s="42">
-        <f t="shared" ref="AB6:AB17" si="15">W6</f>
-        <v>2.6881300304758931</v>
-      </c>
       <c r="AC6" s="43">
-        <f t="shared" ref="AC6:AC18" si="16">S6</f>
+        <f t="shared" ref="AC6:AC12" si="18">S6</f>
         <v>0</v>
       </c>
       <c r="AD6" s="43">
-        <f t="shared" ref="AD6:AD18" si="17">(S6+T6)/2</f>
+        <f t="shared" ref="AD6:AD12" si="19">(S6+T6)/2</f>
         <v>0</v>
       </c>
       <c r="AE6" s="43">
-        <f t="shared" ref="AE6:AE18" si="18">T6</f>
-        <v>0</v>
-      </c>
-      <c r="AF6" s="76">
-        <f t="shared" ref="AF6:AF18" si="19">AE6</f>
+        <f t="shared" ref="AE6:AE12" si="20">T6</f>
+        <v>0</v>
+      </c>
+      <c r="AF6" s="73">
+        <f t="shared" ref="AF6:AF13" si="21">AE6</f>
         <v>0</v>
       </c>
     </row>
@@ -4534,39 +4531,39 @@
         <v>16.800812690474331</v>
       </c>
       <c r="X7" s="43">
-        <f>N7</f>
+        <f t="shared" si="13"/>
+        <v>12.963626223585813</v>
+      </c>
+      <c r="Y7" s="43">
+        <f t="shared" si="14"/>
+        <v>9.5448254250124034</v>
+      </c>
+      <c r="Z7" s="43">
+        <f t="shared" si="15"/>
+        <v>8.4519223209371823</v>
+      </c>
+      <c r="AA7" s="73">
+        <f t="shared" si="16"/>
+        <v>8.4519223209371823</v>
+      </c>
+      <c r="AB7" s="43">
+        <f t="shared" si="17"/>
         <v>16.800812690474331</v>
       </c>
-      <c r="Y7" s="43">
-        <f t="shared" si="3"/>
-        <v>19.089650850024807</v>
-      </c>
-      <c r="Z7" s="43">
-        <f t="shared" si="3"/>
-        <v>16.903844641874365</v>
-      </c>
-      <c r="AA7" s="76">
-        <f t="shared" si="14"/>
-        <v>16.903844641874365</v>
-      </c>
-      <c r="AB7" s="42">
-        <f t="shared" si="15"/>
-        <v>16.800812690474331</v>
-      </c>
       <c r="AC7" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>13.254201084237993</v>
       </c>
       <c r="AD7" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>14.91384967080074</v>
       </c>
       <c r="AE7" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>16.573498257363489</v>
       </c>
-      <c r="AF7" s="76">
-        <f t="shared" si="19"/>
+      <c r="AF7" s="73">
+        <f t="shared" si="21"/>
         <v>16.573498257363489</v>
       </c>
     </row>
@@ -4636,38 +4633,38 @@
       </c>
       <c r="X8" s="43">
         <f t="shared" si="13"/>
+        <v>1.960094813888672</v>
+      </c>
+      <c r="Y8" s="43">
+        <f t="shared" si="14"/>
+        <v>3.2003238189747476</v>
+      </c>
+      <c r="Z8" s="43">
+        <f t="shared" si="15"/>
+        <v>2.1974998034436672</v>
+      </c>
+      <c r="AA8" s="73">
+        <f t="shared" si="16"/>
+        <v>2.1974998034436672</v>
+      </c>
+      <c r="AB8" s="43">
+        <f t="shared" si="17"/>
         <v>3.920189627777344</v>
       </c>
-      <c r="Y8" s="43">
-        <f t="shared" si="3"/>
-        <v>6.4006476379494952</v>
-      </c>
-      <c r="Z8" s="43">
-        <f t="shared" si="3"/>
-        <v>4.3949996068873345</v>
-      </c>
-      <c r="AA8" s="76">
-        <f t="shared" si="14"/>
-        <v>4.3949996068873345</v>
-      </c>
-      <c r="AB8" s="42">
-        <f t="shared" si="15"/>
-        <v>3.920189627777344</v>
-      </c>
       <c r="AC8" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>5.1156565588286975</v>
       </c>
       <c r="AD8" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>8.3761840506164251</v>
       </c>
       <c r="AE8" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>11.636711542404154</v>
       </c>
-      <c r="AF8" s="76">
-        <f t="shared" si="19"/>
+      <c r="AF8" s="73">
+        <f t="shared" si="21"/>
         <v>11.636711542404154</v>
       </c>
     </row>
@@ -4734,35 +4731,35 @@
         <v>0</v>
       </c>
       <c r="Y9" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z9" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA9" s="76">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AB9" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="AA9" s="73">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AB9" s="43">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AC9" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>8.2737362949343645</v>
       </c>
       <c r="AD9" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4.1368681474671822</v>
       </c>
       <c r="AE9" s="43">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AF9" s="76">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AF9" s="73">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -4829,35 +4826,35 @@
         <v>0</v>
       </c>
       <c r="Y10" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z10" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA10" s="76">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AB10" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="AA10" s="73">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AB10" s="43">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AC10" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>3.6907353080344469</v>
       </c>
       <c r="AD10" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>4.021954820011894</v>
       </c>
       <c r="AE10" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>4.3531743319893401</v>
       </c>
-      <c r="AF10" s="76">
-        <f t="shared" si="19"/>
+      <c r="AF10" s="73">
+        <f t="shared" si="21"/>
         <v>4.3531743319893401</v>
       </c>
     </row>
@@ -4927,38 +4924,38 @@
       </c>
       <c r="X11" s="43">
         <f t="shared" si="13"/>
+        <v>24.343208405260931</v>
+      </c>
+      <c r="Y11" s="43">
+        <f t="shared" si="14"/>
+        <v>21.742772443376154</v>
+      </c>
+      <c r="Z11" s="43">
+        <f t="shared" si="15"/>
+        <v>19.824838165705017</v>
+      </c>
+      <c r="AA11" s="73">
+        <f t="shared" si="16"/>
+        <v>19.824838165705017</v>
+      </c>
+      <c r="AB11" s="43">
+        <f t="shared" si="17"/>
         <v>27.048006043083014</v>
       </c>
-      <c r="Y11" s="43">
-        <f t="shared" si="3"/>
-        <v>23.785025983861281</v>
-      </c>
-      <c r="Z11" s="43">
-        <f t="shared" si="3"/>
-        <v>19.949157428519012</v>
-      </c>
-      <c r="AA11" s="76">
-        <f t="shared" si="14"/>
-        <v>19.949157428519012</v>
-      </c>
-      <c r="AB11" s="42">
-        <f t="shared" si="15"/>
-        <v>27.048006043083014</v>
-      </c>
       <c r="AC11" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>0</v>
       </c>
       <c r="AD11" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>0</v>
       </c>
       <c r="AE11" s="43">
-        <f t="shared" si="18"/>
-        <v>0</v>
-      </c>
-      <c r="AF11" s="76">
-        <f t="shared" si="19"/>
+        <f t="shared" si="20"/>
+        <v>0</v>
+      </c>
+      <c r="AF11" s="73">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -5025,35 +5022,35 @@
         <v>0</v>
       </c>
       <c r="Y12" s="43">
-        <f t="shared" si="3"/>
+        <f t="shared" si="14"/>
         <v>0</v>
       </c>
       <c r="Z12" s="43">
-        <f t="shared" si="3"/>
-        <v>0</v>
-      </c>
-      <c r="AA12" s="76">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AB12" s="42">
         <f t="shared" si="15"/>
         <v>0</v>
       </c>
+      <c r="AA12" s="73">
+        <f t="shared" si="16"/>
+        <v>0</v>
+      </c>
+      <c r="AB12" s="43">
+        <f t="shared" si="17"/>
+        <v>0</v>
+      </c>
       <c r="AC12" s="43">
-        <f t="shared" si="16"/>
+        <f t="shared" si="18"/>
         <v>2.3523367897362411</v>
       </c>
       <c r="AD12" s="43">
-        <f t="shared" si="17"/>
+        <f t="shared" si="19"/>
         <v>2.3652615404978614</v>
       </c>
       <c r="AE12" s="43">
-        <f t="shared" si="18"/>
+        <f t="shared" si="20"/>
         <v>2.3781862912594818</v>
       </c>
-      <c r="AF12" s="76">
-        <f t="shared" si="19"/>
+      <c r="AF12" s="73">
+        <f t="shared" si="21"/>
         <v>2.3781862912594818</v>
       </c>
     </row>
@@ -5116,23 +5113,23 @@
         <v>0</v>
       </c>
       <c r="X13" s="43">
-        <f>N13+N14</f>
-        <v>0</v>
+        <f>(N13+Q13+N14+Q14)/2</f>
+        <v>1.7471204866054095</v>
       </c>
       <c r="Y13" s="43">
-        <f t="shared" ref="Y13:Z13" si="20">O13+O14</f>
-        <v>0</v>
+        <f>(O13+R13+O14+R14)/2</f>
+        <v>1.3343217197924386</v>
       </c>
       <c r="Z13" s="43">
-        <f t="shared" si="20"/>
-        <v>0</v>
-      </c>
-      <c r="AA13" s="76">
-        <f t="shared" si="14"/>
-        <v>0</v>
-      </c>
-      <c r="AB13" s="42">
-        <f t="shared" si="15"/>
+        <f>(P13+R13+P14+R14)/2</f>
+        <v>1.3343217197924386</v>
+      </c>
+      <c r="AA13" s="73">
+        <f t="shared" si="16"/>
+        <v>1.3343217197924386</v>
+      </c>
+      <c r="AB13" s="43">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC13" s="43">
@@ -5147,8 +5144,8 @@
         <f>T13+T14</f>
         <v>0</v>
       </c>
-      <c r="AF13" s="76">
-        <f t="shared" si="19"/>
+      <c r="AF13" s="73">
+        <f t="shared" si="21"/>
         <v>0</v>
       </c>
     </row>
@@ -5211,23 +5208,23 @@
         <v>0</v>
       </c>
       <c r="X14" s="43">
-        <f>N15</f>
+        <f>(N15+Q15)/2</f>
         <v>0</v>
       </c>
       <c r="Y14" s="43">
-        <f t="shared" ref="Y14:Z17" si="21">O15</f>
-        <v>2.7576841720418876</v>
+        <f>(O15+R15)/2</f>
+        <v>1.3788420860209438</v>
       </c>
       <c r="Z14" s="43">
-        <f t="shared" si="21"/>
-        <v>5.7656524359881551</v>
-      </c>
-      <c r="AA14" s="76">
+        <f>(P15+R15)/2</f>
+        <v>2.8828262179940776</v>
+      </c>
+      <c r="AA14" s="73">
         <f>Z14</f>
-        <v>5.7656524359881551</v>
-      </c>
-      <c r="AB14" s="42">
-        <f t="shared" si="15"/>
+        <v>2.8828262179940776</v>
+      </c>
+      <c r="AB14" s="43">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC14" s="43">
@@ -5242,7 +5239,7 @@
         <f>T15</f>
         <v>0</v>
       </c>
-      <c r="AF14" s="76">
+      <c r="AF14" s="73">
         <f>AE14</f>
         <v>0</v>
       </c>
@@ -5308,23 +5305,23 @@
         <v>5.8607486129561623</v>
       </c>
       <c r="X15" s="43">
-        <f t="shared" ref="X15:X17" si="23">N16</f>
-        <v>5.8607486129561623</v>
+        <f t="shared" ref="X15:X17" si="23">(N16+Q16)/2</f>
+        <v>5.5834091194714803</v>
       </c>
       <c r="Y15" s="43">
-        <f t="shared" si="21"/>
-        <v>5.7451753584205987</v>
+        <f t="shared" ref="Y15:Y17" si="24">(O16+R16)/2</f>
+        <v>5.5412311187951762</v>
       </c>
       <c r="Z15" s="43">
-        <f t="shared" si="21"/>
-        <v>4.9794271038079518</v>
-      </c>
-      <c r="AA15" s="76">
+        <f t="shared" ref="Z15:Z17" si="25">(P16+R16)/2</f>
+        <v>5.1583569914888532</v>
+      </c>
+      <c r="AA15" s="73">
         <f>Z15</f>
-        <v>4.9794271038079518</v>
-      </c>
-      <c r="AB15" s="42">
-        <f t="shared" si="15"/>
+        <v>5.1583569914888532</v>
+      </c>
+      <c r="AB15" s="43">
+        <f t="shared" si="17"/>
         <v>5.8607486129561623</v>
       </c>
       <c r="AC15" s="43">
@@ -5339,7 +5336,7 @@
         <f>T16</f>
         <v>0</v>
       </c>
-      <c r="AF15" s="76">
+      <c r="AF15" s="73">
         <f>AE15</f>
         <v>0</v>
       </c>
@@ -5413,19 +5410,19 @@
         <v>0</v>
       </c>
       <c r="Y16" s="43">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z16" s="43">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AA16" s="76">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AA16" s="73">
         <f>Z16</f>
         <v>0</v>
       </c>
-      <c r="AB16" s="42">
-        <f t="shared" si="15"/>
+      <c r="AB16" s="43">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC16" s="43">
@@ -5440,7 +5437,7 @@
         <f>T17</f>
         <v>7.4625845691245809</v>
       </c>
-      <c r="AF16" s="76">
+      <c r="AF16" s="73">
         <f>AE16</f>
         <v>7.4625845691245809</v>
       </c>
@@ -5508,19 +5505,19 @@
         <v>0</v>
       </c>
       <c r="Y17" s="46">
-        <f t="shared" si="21"/>
+        <f t="shared" si="24"/>
         <v>0</v>
       </c>
       <c r="Z17" s="46">
-        <f t="shared" si="21"/>
-        <v>0</v>
-      </c>
-      <c r="AA17" s="77">
+        <f t="shared" si="25"/>
+        <v>0</v>
+      </c>
+      <c r="AA17" s="74">
         <f>Z17</f>
         <v>0</v>
       </c>
-      <c r="AB17" s="45">
-        <f t="shared" si="15"/>
+      <c r="AB17" s="46">
+        <f t="shared" si="17"/>
         <v>0</v>
       </c>
       <c r="AC17" s="46">
@@ -5535,7 +5532,7 @@
         <f>T18</f>
         <v>0</v>
       </c>
-      <c r="AF17" s="77">
+      <c r="AF17" s="74">
         <f>AE17</f>
         <v>0</v>
       </c>
@@ -5634,43 +5631,43 @@
       <c r="V19" s="57" t="s">
         <v>98</v>
       </c>
-      <c r="W19" s="72">
+      <c r="W19" s="69">
         <f>(550+1650+2800)/1000/(15-0+1)*52*F24</f>
         <v>14.427074999999999</v>
       </c>
-      <c r="X19" s="73">
-        <f>F31</f>
-        <v>31.390907416054425</v>
-      </c>
-      <c r="Y19" s="73">
-        <f>G31</f>
-        <v>37.754740931981566</v>
-      </c>
-      <c r="Z19" s="73">
+      <c r="X19" s="70">
+        <f>(F31+I31)/2</f>
+        <v>35.955136032867976</v>
+      </c>
+      <c r="Y19" s="70">
+        <f>(G31+J31)/2</f>
+        <v>31.729574287646834</v>
+      </c>
+      <c r="Z19" s="70">
         <f>H31</f>
         <v>36.30498550425397</v>
       </c>
-      <c r="AA19" s="78">
+      <c r="AA19" s="75">
         <f>48/448*365.25/(1+1/12.5)</f>
         <v>36.235119047619044</v>
       </c>
-      <c r="AB19" s="72">
+      <c r="AB19" s="69">
         <f>W19</f>
         <v>14.427074999999999</v>
       </c>
-      <c r="AC19" s="73">
+      <c r="AC19" s="70">
         <f>K31</f>
         <v>31.765466750719003</v>
       </c>
-      <c r="AD19" s="73">
+      <c r="AD19" s="70">
         <f>(K31+L31)/2</f>
         <v>34.907873896644638</v>
       </c>
-      <c r="AE19" s="73">
+      <c r="AE19" s="70">
         <f>L31</f>
         <v>38.050281042570276</v>
       </c>
-      <c r="AF19" s="78">
+      <c r="AF19" s="75">
         <f>AA19</f>
         <v>36.235119047619044</v>
       </c>
@@ -5754,9 +5751,7 @@
       <c r="S21" s="4"/>
       <c r="T21" s="4"/>
       <c r="U21" s="4"/>
-      <c r="W21" s="8" t="s">
-        <v>118</v>
-      </c>
+      <c r="W21" s="8"/>
     </row>
     <row r="22" spans="2:32" x14ac:dyDescent="0.25">
       <c r="B22" t="s">
@@ -5823,11 +5818,11 @@
         <v>0.79860000000000009</v>
       </c>
       <c r="K24" s="33">
-        <f t="shared" ref="K24:L24" si="24">SUMPRODUCT(K$5:K$22/100,$D$5:$D$22)</f>
+        <f t="shared" ref="K24:L24" si="26">SUMPRODUCT(K$5:K$22/100,$D$5:$D$22)</f>
         <v>0.86208999999999991</v>
       </c>
       <c r="L24" s="35">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>0.85735000000000006</v>
       </c>
     </row>
@@ -5840,27 +5835,27 @@
         <v>0.76781999999999995</v>
       </c>
       <c r="G25" s="37">
-        <f t="shared" ref="G25:L25" si="25">SUMPRODUCT(G$5:G$18/100,$D$5:$D$18)</f>
+        <f t="shared" ref="G25:L25" si="27">SUMPRODUCT(G$5:G$18/100,$D$5:$D$18)</f>
         <v>0.76585999999999999</v>
       </c>
       <c r="H25" s="37">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.76313999999999993</v>
       </c>
       <c r="I25" s="37">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.77270000000000005</v>
       </c>
       <c r="J25" s="37">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.6745000000000001</v>
       </c>
       <c r="K25" s="36">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.73968999999999996</v>
       </c>
       <c r="L25" s="38">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>0.73165000000000002</v>
       </c>
     </row>
@@ -5977,27 +5972,27 @@
         <v>31.390907416054425</v>
       </c>
       <c r="G31" s="46">
-        <f t="shared" ref="G31:J31" si="26">G30*G24</f>
+        <f t="shared" ref="G31:J31" si="28">G30*G24</f>
         <v>37.754740931981566</v>
       </c>
       <c r="H31" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>36.30498550425397</v>
       </c>
       <c r="I31" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>40.519364649681528</v>
       </c>
       <c r="J31" s="46">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>25.704407643312106</v>
       </c>
       <c r="K31" s="45">
-        <f t="shared" ref="K31" si="27">K30*K24</f>
+        <f t="shared" ref="K31" si="29">K30*K24</f>
         <v>31.765466750719003</v>
       </c>
       <c r="L31" s="47">
-        <f t="shared" ref="L31" si="28">L30*L24</f>
+        <f t="shared" ref="L31" si="30">L30*L24</f>
         <v>38.050281042570276</v>
       </c>
     </row>

--- a/data/prod_parameters/LayerHerd.xlsx
+++ b/data/prod_parameters/LayerHerd.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12300"/>
   </bookViews>
   <sheets>
     <sheet name="default" sheetId="2" r:id="rId1"/>
@@ -62,7 +62,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="118">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="726" uniqueCount="120">
   <si>
     <t>value</t>
   </si>
@@ -416,6 +416,12 @@
   </si>
   <si>
     <t>share_in_ration</t>
+  </si>
+  <si>
+    <t>Creates problems with too much poultry meat</t>
+  </si>
+  <si>
+    <t>Slaughter and live weights</t>
   </si>
 </sst>
 </file>
@@ -1078,7 +1084,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:H173"/>
+  <dimension ref="A1:H176"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="15.7109375" customWidth="1"/>
@@ -1490,79 +1496,59 @@
         <v>kg/head/year</v>
       </c>
     </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="C26" s="8"/>
+      <c r="E26" s="15"/>
+      <c r="F26" s="15"/>
+    </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="D27" t="s">
+      <c r="A27" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="B27" s="6"/>
+      <c r="C27" s="6"/>
+      <c r="D27" s="6"/>
+      <c r="E27" s="6"/>
+      <c r="F27" s="6"/>
+      <c r="G27" s="6"/>
+      <c r="H27" s="6"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="D28" t="s">
         <v>14</v>
       </c>
-      <c r="E27" s="8">
-        <v>0</v>
-      </c>
-      <c r="F27" t="s">
+      <c r="E28" s="8">
+        <v>0</v>
+      </c>
+      <c r="F28" t="s">
         <v>15</v>
       </c>
-      <c r="G27" s="8" t="s">
-        <v>52</v>
+      <c r="G28" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
     <row r="29" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A29" s="6" t="s">
+      <c r="E29" s="8"/>
+      <c r="G29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E30" s="8"/>
+      <c r="G30" s="8"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A32" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-      <c r="D29" s="6"/>
-      <c r="E29" s="6"/>
-      <c r="F29" s="71" t="s">
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+      <c r="D32" s="6"/>
+      <c r="E32" s="6"/>
+      <c r="F32" s="71" t="s">
         <v>112</v>
       </c>
-      <c r="G29" s="6"/>
-      <c r="H29" s="71" t="s">
+      <c r="G32" s="6"/>
+      <c r="H32" s="71" t="s">
         <v>115</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" t="s">
-        <v>41</v>
-      </c>
-      <c r="B30" t="s">
-        <v>47</v>
-      </c>
-      <c r="D30" t="s">
-        <v>116</v>
-      </c>
-      <c r="E30" s="4">
-        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B30,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>14.427074999999999</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" t="s">
-        <v>41</v>
-      </c>
-      <c r="B31" t="s">
-        <v>48</v>
-      </c>
-      <c r="D31" t="s">
-        <v>116</v>
-      </c>
-      <c r="E31" s="4">
-        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B31,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>35.955136032867976</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A32" t="s">
-        <v>41</v>
-      </c>
-      <c r="B32" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" t="s">
-        <v>116</v>
-      </c>
-      <c r="E32" s="4">
-        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B32,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>31.729574287646834</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1570,14 +1556,14 @@
         <v>41</v>
       </c>
       <c r="B33" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D33" t="s">
         <v>116</v>
       </c>
       <c r="E33" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B33,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>36.30498550425397</v>
+        <v>14.427074999999999</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -1585,59 +1571,59 @@
         <v>41</v>
       </c>
       <c r="B34" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="D34" t="s">
         <v>116</v>
       </c>
       <c r="E34" s="4">
         <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B34,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>36.235119047619044</v>
+        <v>35.955136032867976</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A35" t="s">
+        <v>41</v>
+      </c>
+      <c r="B35" t="s">
+        <v>49</v>
+      </c>
+      <c r="D35" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="4">
+        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B35,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>31.729574287646834</v>
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B36" t="s">
-        <v>47</v>
+        <v>50</v>
       </c>
       <c r="D36" t="s">
         <v>116</v>
       </c>
       <c r="E36" s="4">
-        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B36,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>14.427074999999999</v>
+        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B36,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>36.30498550425397</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B37" t="s">
-        <v>48</v>
+        <v>94</v>
       </c>
       <c r="D37" t="s">
         <v>116</v>
       </c>
       <c r="E37" s="4">
-        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B37,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>31.765466750719003</v>
-      </c>
-    </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A38" t="s">
-        <v>42</v>
-      </c>
-      <c r="B38" t="s">
-        <v>49</v>
-      </c>
-      <c r="D38" t="s">
-        <v>116</v>
-      </c>
-      <c r="E38" s="4">
-        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B38,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>34.907873896644638</v>
+        <f>INDEX('Feed rations'!$W$19:$AA$19,MATCH(B37,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>36.235119047619044</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1645,14 +1631,14 @@
         <v>42</v>
       </c>
       <c r="B39" t="s">
-        <v>50</v>
+        <v>47</v>
       </c>
       <c r="D39" t="s">
         <v>116</v>
       </c>
       <c r="E39" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B39,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>38.050281042570276</v>
+        <v>14.427074999999999</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1660,84 +1646,75 @@
         <v>42</v>
       </c>
       <c r="B40" t="s">
-        <v>94</v>
+        <v>48</v>
       </c>
       <c r="D40" t="s">
         <v>116</v>
       </c>
       <c r="E40" s="4">
         <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B40,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>36.235119047619044</v>
+        <v>31.765466750719003</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A41" t="s">
+        <v>42</v>
+      </c>
+      <c r="B41" t="s">
+        <v>49</v>
+      </c>
+      <c r="D41" t="s">
+        <v>116</v>
+      </c>
+      <c r="E41" s="4">
+        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B41,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>34.907873896644638</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A42" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="B42" s="6"/>
-      <c r="C42" s="6"/>
-      <c r="D42" s="6"/>
-      <c r="E42" s="6"/>
-      <c r="F42" s="71" t="s">
-        <v>114</v>
-      </c>
-      <c r="G42" s="6"/>
-      <c r="H42" s="71" t="s">
-        <v>115</v>
+      <c r="A42" t="s">
+        <v>42</v>
+      </c>
+      <c r="B42" t="s">
+        <v>50</v>
+      </c>
+      <c r="D42" t="s">
+        <v>116</v>
+      </c>
+      <c r="E42" s="4">
+        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B42,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>38.050281042570276</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>47</v>
-      </c>
-      <c r="C43" t="s">
-        <v>17</v>
+        <v>94</v>
       </c>
       <c r="D43" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="E43" s="4">
-        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C43,'Feed rations'!$V$5:$V$17,0),MATCH(B43,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>43.682112995233247</v>
-      </c>
-    </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A44" t="s">
-        <v>41</v>
-      </c>
-      <c r="B44" t="s">
-        <v>47</v>
-      </c>
-      <c r="C44" t="s">
-        <v>19</v>
-      </c>
-      <c r="D44" t="s">
-        <v>117</v>
-      </c>
-      <c r="E44" s="4">
-        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C44,'Feed rations'!$V$5:$V$17,0),MATCH(B44,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.6881300304758931</v>
+        <f>INDEX('Feed rations'!$AB$19:$AF$19,MATCH(B43,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>36.235119047619044</v>
       </c>
     </row>
     <row r="45" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A45" t="s">
-        <v>41</v>
-      </c>
-      <c r="B45" t="s">
-        <v>47</v>
-      </c>
-      <c r="C45" t="s">
-        <v>18</v>
-      </c>
-      <c r="D45" t="s">
-        <v>117</v>
-      </c>
-      <c r="E45" s="4">
-        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C45,'Feed rations'!$V$5:$V$17,0),MATCH(B45,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>16.800812690474331</v>
+      <c r="A45" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="B45" s="6"/>
+      <c r="C45" s="6"/>
+      <c r="D45" s="6"/>
+      <c r="E45" s="6"/>
+      <c r="F45" s="71" t="s">
+        <v>114</v>
+      </c>
+      <c r="G45" s="6"/>
+      <c r="H45" s="71" t="s">
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1748,14 +1725,14 @@
         <v>47</v>
       </c>
       <c r="C46" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D46" t="s">
         <v>117</v>
       </c>
       <c r="E46" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C46,'Feed rations'!$V$5:$V$17,0),MATCH(B46,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>3.920189627777344</v>
+        <v>43.682112995233247</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -1766,14 +1743,14 @@
         <v>47</v>
       </c>
       <c r="C47" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D47" t="s">
         <v>117</v>
       </c>
       <c r="E47" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C47,'Feed rations'!$V$5:$V$17,0),MATCH(B47,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>2.6881300304758931</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -1784,14 +1761,14 @@
         <v>47</v>
       </c>
       <c r="C48" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D48" t="s">
         <v>117</v>
       </c>
       <c r="E48" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C48,'Feed rations'!$V$5:$V$17,0),MATCH(B48,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>16.800812690474331</v>
       </c>
     </row>
     <row r="49" spans="1:5" x14ac:dyDescent="0.25">
@@ -1802,14 +1779,14 @@
         <v>47</v>
       </c>
       <c r="C49" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D49" t="s">
         <v>117</v>
       </c>
       <c r="E49" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C49,'Feed rations'!$V$5:$V$17,0),MATCH(B49,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>27.048006043083014</v>
+        <v>3.920189627777344</v>
       </c>
     </row>
     <row r="50" spans="1:5" x14ac:dyDescent="0.25">
@@ -1820,7 +1797,7 @@
         <v>47</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D50" t="s">
         <v>117</v>
@@ -1838,7 +1815,7 @@
         <v>47</v>
       </c>
       <c r="C51" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D51" t="s">
         <v>117</v>
@@ -1856,14 +1833,14 @@
         <v>47</v>
       </c>
       <c r="C52" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D52" t="s">
         <v>117</v>
       </c>
       <c r="E52" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C52,'Feed rations'!$V$5:$V$17,0),MATCH(B52,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>27.048006043083014</v>
       </c>
     </row>
     <row r="53" spans="1:5" x14ac:dyDescent="0.25">
@@ -1874,14 +1851,14 @@
         <v>47</v>
       </c>
       <c r="C53" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D53" t="s">
         <v>117</v>
       </c>
       <c r="E53" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C53,'Feed rations'!$V$5:$V$17,0),MATCH(B53,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.8607486129561623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:5" x14ac:dyDescent="0.25">
@@ -1892,7 +1869,7 @@
         <v>47</v>
       </c>
       <c r="C54" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D54" t="s">
         <v>117</v>
@@ -1910,7 +1887,7 @@
         <v>47</v>
       </c>
       <c r="C55" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D55" t="s">
         <v>117</v>
@@ -1925,17 +1902,17 @@
         <v>41</v>
       </c>
       <c r="B56" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C56" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D56" t="s">
         <v>117</v>
       </c>
       <c r="E56" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C56,'Feed rations'!$V$5:$V$17,0),MATCH(B56,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>52.05847593594973</v>
+        <v>5.8607486129561623</v>
       </c>
     </row>
     <row r="57" spans="1:5" x14ac:dyDescent="0.25">
@@ -1943,17 +1920,17 @@
         <v>41</v>
       </c>
       <c r="B57" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C57" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D57" t="s">
         <v>117</v>
       </c>
       <c r="E57" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C57,'Feed rations'!$V$5:$V$17,0),MATCH(B57,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3440650152379465</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:5" x14ac:dyDescent="0.25">
@@ -1961,17 +1938,17 @@
         <v>41</v>
       </c>
       <c r="B58" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C58" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D58" t="s">
         <v>117</v>
       </c>
       <c r="E58" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C58,'Feed rations'!$V$5:$V$17,0),MATCH(B58,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>12.963626223585813</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:5" x14ac:dyDescent="0.25">
@@ -1982,14 +1959,14 @@
         <v>48</v>
       </c>
       <c r="C59" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D59" t="s">
         <v>117</v>
       </c>
       <c r="E59" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C59,'Feed rations'!$V$5:$V$17,0),MATCH(B59,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.960094813888672</v>
+        <v>52.05847593594973</v>
       </c>
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.25">
@@ -2000,14 +1977,14 @@
         <v>48</v>
       </c>
       <c r="C60" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D60" t="s">
         <v>117</v>
       </c>
       <c r="E60" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C60,'Feed rations'!$V$5:$V$17,0),MATCH(B60,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3440650152379465</v>
       </c>
     </row>
     <row r="61" spans="1:5" x14ac:dyDescent="0.25">
@@ -2018,14 +1995,14 @@
         <v>48</v>
       </c>
       <c r="C61" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D61" t="s">
         <v>117</v>
       </c>
       <c r="E61" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C61,'Feed rations'!$V$5:$V$17,0),MATCH(B61,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>12.963626223585813</v>
       </c>
     </row>
     <row r="62" spans="1:5" x14ac:dyDescent="0.25">
@@ -2036,14 +2013,14 @@
         <v>48</v>
       </c>
       <c r="C62" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D62" t="s">
         <v>117</v>
       </c>
       <c r="E62" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C62,'Feed rations'!$V$5:$V$17,0),MATCH(B62,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>24.343208405260931</v>
+        <v>1.960094813888672</v>
       </c>
     </row>
     <row r="63" spans="1:5" x14ac:dyDescent="0.25">
@@ -2054,7 +2031,7 @@
         <v>48</v>
       </c>
       <c r="C63" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D63" t="s">
         <v>117</v>
@@ -2072,14 +2049,14 @@
         <v>48</v>
       </c>
       <c r="C64" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D64" t="s">
         <v>117</v>
       </c>
       <c r="E64" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C64,'Feed rations'!$V$5:$V$17,0),MATCH(B64,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.7471204866054095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:5" x14ac:dyDescent="0.25">
@@ -2090,14 +2067,14 @@
         <v>48</v>
       </c>
       <c r="C65" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D65" t="s">
         <v>117</v>
       </c>
       <c r="E65" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C65,'Feed rations'!$V$5:$V$17,0),MATCH(B65,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>24.343208405260931</v>
       </c>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.25">
@@ -2108,14 +2085,14 @@
         <v>48</v>
       </c>
       <c r="C66" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D66" t="s">
         <v>117</v>
       </c>
       <c r="E66" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C66,'Feed rations'!$V$5:$V$17,0),MATCH(B66,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.5834091194714803</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:5" x14ac:dyDescent="0.25">
@@ -2126,14 +2103,14 @@
         <v>48</v>
       </c>
       <c r="C67" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D67" t="s">
         <v>117</v>
       </c>
       <c r="E67" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C67,'Feed rations'!$V$5:$V$17,0),MATCH(B67,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.7471204866054095</v>
       </c>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.25">
@@ -2144,7 +2121,7 @@
         <v>48</v>
       </c>
       <c r="C68" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D68" t="s">
         <v>117</v>
@@ -2159,17 +2136,17 @@
         <v>41</v>
       </c>
       <c r="B69" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D69" t="s">
         <v>117</v>
       </c>
       <c r="E69" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C69,'Feed rations'!$V$5:$V$17,0),MATCH(B69,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>55.910178622144024</v>
+        <v>5.5834091194714803</v>
       </c>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.25">
@@ -2177,17 +2154,17 @@
         <v>41</v>
       </c>
       <c r="B70" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C70" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D70" t="s">
         <v>117</v>
       </c>
       <c r="E70" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C70,'Feed rations'!$V$5:$V$17,0),MATCH(B70,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3475047658841042</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.25">
@@ -2195,17 +2172,17 @@
         <v>41</v>
       </c>
       <c r="B71" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C71" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D71" t="s">
         <v>117</v>
       </c>
       <c r="E71" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C71,'Feed rations'!$V$5:$V$17,0),MATCH(B71,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>9.5448254250124034</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.25">
@@ -2216,14 +2193,14 @@
         <v>49</v>
       </c>
       <c r="C72" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D72" t="s">
         <v>117</v>
       </c>
       <c r="E72" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C72,'Feed rations'!$V$5:$V$17,0),MATCH(B72,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>3.2003238189747476</v>
+        <v>55.910178622144024</v>
       </c>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.25">
@@ -2234,14 +2211,14 @@
         <v>49</v>
       </c>
       <c r="C73" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D73" t="s">
         <v>117</v>
       </c>
       <c r="E73" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C73,'Feed rations'!$V$5:$V$17,0),MATCH(B73,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3475047658841042</v>
       </c>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.25">
@@ -2252,14 +2229,14 @@
         <v>49</v>
       </c>
       <c r="C74" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D74" t="s">
         <v>117</v>
       </c>
       <c r="E74" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C74,'Feed rations'!$V$5:$V$17,0),MATCH(B74,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>9.5448254250124034</v>
       </c>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.25">
@@ -2270,14 +2247,14 @@
         <v>49</v>
       </c>
       <c r="C75" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D75" t="s">
         <v>117</v>
       </c>
       <c r="E75" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C75,'Feed rations'!$V$5:$V$17,0),MATCH(B75,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>21.742772443376154</v>
+        <v>3.2003238189747476</v>
       </c>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.25">
@@ -2288,7 +2265,7 @@
         <v>49</v>
       </c>
       <c r="C76" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D76" t="s">
         <v>117</v>
@@ -2306,14 +2283,14 @@
         <v>49</v>
       </c>
       <c r="C77" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D77" t="s">
         <v>117</v>
       </c>
       <c r="E77" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C77,'Feed rations'!$V$5:$V$17,0),MATCH(B77,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.25">
@@ -2324,14 +2301,14 @@
         <v>49</v>
       </c>
       <c r="C78" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D78" t="s">
         <v>117</v>
       </c>
       <c r="E78" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C78,'Feed rations'!$V$5:$V$17,0),MATCH(B78,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3788420860209438</v>
+        <v>21.742772443376154</v>
       </c>
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.25">
@@ -2342,14 +2319,14 @@
         <v>49</v>
       </c>
       <c r="C79" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D79" t="s">
         <v>117</v>
       </c>
       <c r="E79" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C79,'Feed rations'!$V$5:$V$17,0),MATCH(B79,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.5412311187951762</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.25">
@@ -2360,14 +2337,14 @@
         <v>49</v>
       </c>
       <c r="C80" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D80" t="s">
         <v>117</v>
       </c>
       <c r="E80" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C80,'Feed rations'!$V$5:$V$17,0),MATCH(B80,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="81" spans="1:5" x14ac:dyDescent="0.25">
@@ -2378,14 +2355,14 @@
         <v>49</v>
       </c>
       <c r="C81" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D81" t="s">
         <v>117</v>
       </c>
       <c r="E81" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C81,'Feed rations'!$V$5:$V$17,0),MATCH(B81,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3788420860209438</v>
       </c>
     </row>
     <row r="82" spans="1:5" x14ac:dyDescent="0.25">
@@ -2393,17 +2370,17 @@
         <v>41</v>
       </c>
       <c r="B82" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D82" t="s">
         <v>117</v>
       </c>
       <c r="E82" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C82,'Feed rations'!$V$5:$V$17,0),MATCH(B82,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>58.797927209288808</v>
+        <v>5.5412311187951762</v>
       </c>
     </row>
     <row r="83" spans="1:5" x14ac:dyDescent="0.25">
@@ -2411,17 +2388,17 @@
         <v>41</v>
       </c>
       <c r="B83" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C83" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D83" t="s">
         <v>117</v>
       </c>
       <c r="E83" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C83,'Feed rations'!$V$5:$V$17,0),MATCH(B83,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3523075713499491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:5" x14ac:dyDescent="0.25">
@@ -2429,17 +2406,17 @@
         <v>41</v>
       </c>
       <c r="B84" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C84" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D84" t="s">
         <v>117</v>
       </c>
       <c r="E84" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C84,'Feed rations'!$V$5:$V$17,0),MATCH(B84,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>8.4519223209371823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:5" x14ac:dyDescent="0.25">
@@ -2450,14 +2427,14 @@
         <v>50</v>
       </c>
       <c r="C85" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D85" t="s">
         <v>117</v>
       </c>
       <c r="E85" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C85,'Feed rations'!$V$5:$V$17,0),MATCH(B85,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.1974998034436672</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.25">
@@ -2468,14 +2445,14 @@
         <v>50</v>
       </c>
       <c r="C86" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D86" t="s">
         <v>117</v>
       </c>
       <c r="E86" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C86,'Feed rations'!$V$5:$V$17,0),MATCH(B86,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.25">
@@ -2486,14 +2463,14 @@
         <v>50</v>
       </c>
       <c r="C87" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D87" t="s">
         <v>117</v>
       </c>
       <c r="E87" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C87,'Feed rations'!$V$5:$V$17,0),MATCH(B87,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.25">
@@ -2504,14 +2481,14 @@
         <v>50</v>
       </c>
       <c r="C88" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D88" t="s">
         <v>117</v>
       </c>
       <c r="E88" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C88,'Feed rations'!$V$5:$V$17,0),MATCH(B88,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.824838165705017</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.25">
@@ -2522,7 +2499,7 @@
         <v>50</v>
       </c>
       <c r="C89" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D89" t="s">
         <v>117</v>
@@ -2540,14 +2517,14 @@
         <v>50</v>
       </c>
       <c r="C90" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D90" t="s">
         <v>117</v>
       </c>
       <c r="E90" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C90,'Feed rations'!$V$5:$V$17,0),MATCH(B90,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:5" x14ac:dyDescent="0.25">
@@ -2558,14 +2535,14 @@
         <v>50</v>
       </c>
       <c r="C91" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D91" t="s">
         <v>117</v>
       </c>
       <c r="E91" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C91,'Feed rations'!$V$5:$V$17,0),MATCH(B91,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.8828262179940776</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="92" spans="1:5" x14ac:dyDescent="0.25">
@@ -2576,14 +2553,14 @@
         <v>50</v>
       </c>
       <c r="C92" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D92" t="s">
         <v>117</v>
       </c>
       <c r="E92" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C92,'Feed rations'!$V$5:$V$17,0),MATCH(B92,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.1583569914888532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.25">
@@ -2594,14 +2571,14 @@
         <v>50</v>
       </c>
       <c r="C93" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D93" t="s">
         <v>117</v>
       </c>
       <c r="E93" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C93,'Feed rations'!$V$5:$V$17,0),MATCH(B93,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.25">
@@ -2612,14 +2589,14 @@
         <v>50</v>
       </c>
       <c r="C94" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D94" t="s">
         <v>117</v>
       </c>
       <c r="E94" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C94,'Feed rations'!$V$5:$V$17,0),MATCH(B94,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="95" spans="1:5" x14ac:dyDescent="0.25">
@@ -2627,17 +2604,17 @@
         <v>41</v>
       </c>
       <c r="B95" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D95" t="s">
         <v>117</v>
       </c>
       <c r="E95" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C95,'Feed rations'!$V$5:$V$17,0),MATCH(B95,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>58.797927209288808</v>
+        <v>5.1583569914888532</v>
       </c>
     </row>
     <row r="96" spans="1:5" x14ac:dyDescent="0.25">
@@ -2645,17 +2622,17 @@
         <v>41</v>
       </c>
       <c r="B96" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C96" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D96" t="s">
         <v>117</v>
       </c>
       <c r="E96" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C96,'Feed rations'!$V$5:$V$17,0),MATCH(B96,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3523075713499491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:5" x14ac:dyDescent="0.25">
@@ -2663,17 +2640,17 @@
         <v>41</v>
       </c>
       <c r="B97" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C97" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D97" t="s">
         <v>117</v>
       </c>
       <c r="E97" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C97,'Feed rations'!$V$5:$V$17,0),MATCH(B97,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>8.4519223209371823</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:5" x14ac:dyDescent="0.25">
@@ -2684,14 +2661,14 @@
         <v>94</v>
       </c>
       <c r="C98" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D98" t="s">
         <v>117</v>
       </c>
       <c r="E98" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C98,'Feed rations'!$V$5:$V$17,0),MATCH(B98,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.1974998034436672</v>
+        <v>58.797927209288808</v>
       </c>
     </row>
     <row r="99" spans="1:5" x14ac:dyDescent="0.25">
@@ -2702,14 +2679,14 @@
         <v>94</v>
       </c>
       <c r="C99" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D99" t="s">
         <v>117</v>
       </c>
       <c r="E99" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C99,'Feed rations'!$V$5:$V$17,0),MATCH(B99,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3523075713499491</v>
       </c>
     </row>
     <row r="100" spans="1:5" x14ac:dyDescent="0.25">
@@ -2720,14 +2697,14 @@
         <v>94</v>
       </c>
       <c r="C100" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D100" t="s">
         <v>117</v>
       </c>
       <c r="E100" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C100,'Feed rations'!$V$5:$V$17,0),MATCH(B100,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>8.4519223209371823</v>
       </c>
     </row>
     <row r="101" spans="1:5" x14ac:dyDescent="0.25">
@@ -2738,14 +2715,14 @@
         <v>94</v>
       </c>
       <c r="C101" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D101" t="s">
         <v>117</v>
       </c>
       <c r="E101" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C101,'Feed rations'!$V$5:$V$17,0),MATCH(B101,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>19.824838165705017</v>
+        <v>2.1974998034436672</v>
       </c>
     </row>
     <row r="102" spans="1:5" x14ac:dyDescent="0.25">
@@ -2756,7 +2733,7 @@
         <v>94</v>
       </c>
       <c r="C102" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D102" t="s">
         <v>117</v>
@@ -2774,14 +2751,14 @@
         <v>94</v>
       </c>
       <c r="C103" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D103" t="s">
         <v>117</v>
       </c>
       <c r="E103" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C103,'Feed rations'!$V$5:$V$17,0),MATCH(B103,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>1.3343217197924386</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:5" x14ac:dyDescent="0.25">
@@ -2792,14 +2769,14 @@
         <v>94</v>
       </c>
       <c r="C104" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D104" t="s">
         <v>117</v>
       </c>
       <c r="E104" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C104,'Feed rations'!$V$5:$V$17,0),MATCH(B104,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>2.8828262179940776</v>
+        <v>19.824838165705017</v>
       </c>
     </row>
     <row r="105" spans="1:5" x14ac:dyDescent="0.25">
@@ -2810,14 +2787,14 @@
         <v>94</v>
       </c>
       <c r="C105" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D105" t="s">
         <v>117</v>
       </c>
       <c r="E105" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C105,'Feed rations'!$V$5:$V$17,0),MATCH(B105,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>5.1583569914888532</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:5" x14ac:dyDescent="0.25">
@@ -2828,14 +2805,14 @@
         <v>94</v>
       </c>
       <c r="C106" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D106" t="s">
         <v>117</v>
       </c>
       <c r="E106" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C106,'Feed rations'!$V$5:$V$17,0),MATCH(B106,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>1.3343217197924386</v>
       </c>
     </row>
     <row r="107" spans="1:5" x14ac:dyDescent="0.25">
@@ -2846,72 +2823,72 @@
         <v>94</v>
       </c>
       <c r="C107" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D107" t="s">
         <v>117</v>
       </c>
       <c r="E107" s="4">
         <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C107,'Feed rations'!$V$5:$V$17,0),MATCH(B107,'Feed rations'!$W$4:$AA$4,0))</f>
-        <v>0</v>
+        <v>2.8828262179940776</v>
       </c>
     </row>
     <row r="108" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="E108" s="4"/>
+      <c r="A108" t="s">
+        <v>41</v>
+      </c>
+      <c r="B108" t="s">
+        <v>94</v>
+      </c>
+      <c r="C108" t="s">
+        <v>23</v>
+      </c>
+      <c r="D108" t="s">
+        <v>117</v>
+      </c>
+      <c r="E108" s="4">
+        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C108,'Feed rations'!$V$5:$V$17,0),MATCH(B108,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>5.1583569914888532</v>
+      </c>
     </row>
     <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B109" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C109" t="s">
-        <v>17</v>
+        <v>97</v>
       </c>
       <c r="D109" t="s">
         <v>117</v>
       </c>
       <c r="E109" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C109,'Feed rations'!$V$5:$V$17,0),MATCH(B109,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>43.682112995233247</v>
+        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C109,'Feed rations'!$V$5:$V$17,0),MATCH(B109,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="B110" t="s">
-        <v>47</v>
+        <v>94</v>
       </c>
       <c r="C110" t="s">
-        <v>19</v>
+        <v>27</v>
       </c>
       <c r="D110" t="s">
         <v>117</v>
       </c>
       <c r="E110" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C110,'Feed rations'!$V$5:$V$17,0),MATCH(B110,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.6881300304758931</v>
+        <f>INDEX('Feed rations'!$W$5:$AA$17,MATCH(C110,'Feed rations'!$V$5:$V$17,0),MATCH(B110,'Feed rations'!$W$4:$AA$4,0))</f>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A111" t="s">
-        <v>42</v>
-      </c>
-      <c r="B111" t="s">
-        <v>47</v>
-      </c>
-      <c r="C111" t="s">
-        <v>18</v>
-      </c>
-      <c r="D111" t="s">
-        <v>117</v>
-      </c>
-      <c r="E111" s="4">
-        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C111,'Feed rations'!$V$5:$V$17,0),MATCH(B111,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.800812690474331</v>
-      </c>
+      <c r="E111" s="4"/>
     </row>
     <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
@@ -2921,14 +2898,14 @@
         <v>47</v>
       </c>
       <c r="C112" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D112" t="s">
         <v>117</v>
       </c>
       <c r="E112" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C112,'Feed rations'!$V$5:$V$17,0),MATCH(B112,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>3.920189627777344</v>
+        <v>43.682112995233247</v>
       </c>
     </row>
     <row r="113" spans="1:5" x14ac:dyDescent="0.25">
@@ -2939,14 +2916,14 @@
         <v>47</v>
       </c>
       <c r="C113" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D113" t="s">
         <v>117</v>
       </c>
       <c r="E113" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C113,'Feed rations'!$V$5:$V$17,0),MATCH(B113,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.6881300304758931</v>
       </c>
     </row>
     <row r="114" spans="1:5" x14ac:dyDescent="0.25">
@@ -2957,14 +2934,14 @@
         <v>47</v>
       </c>
       <c r="C114" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D114" t="s">
         <v>117</v>
       </c>
       <c r="E114" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C114,'Feed rations'!$V$5:$V$17,0),MATCH(B114,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>16.800812690474331</v>
       </c>
     </row>
     <row r="115" spans="1:5" x14ac:dyDescent="0.25">
@@ -2975,14 +2952,14 @@
         <v>47</v>
       </c>
       <c r="C115" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D115" t="s">
         <v>117</v>
       </c>
       <c r="E115" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C115,'Feed rations'!$V$5:$V$17,0),MATCH(B115,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>27.048006043083014</v>
+        <v>3.920189627777344</v>
       </c>
     </row>
     <row r="116" spans="1:5" x14ac:dyDescent="0.25">
@@ -2993,7 +2970,7 @@
         <v>47</v>
       </c>
       <c r="C116" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D116" t="s">
         <v>117</v>
@@ -3011,7 +2988,7 @@
         <v>47</v>
       </c>
       <c r="C117" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D117" t="s">
         <v>117</v>
@@ -3029,14 +3006,14 @@
         <v>47</v>
       </c>
       <c r="C118" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D118" t="s">
         <v>117</v>
       </c>
       <c r="E118" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C118,'Feed rations'!$V$5:$V$17,0),MATCH(B118,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>27.048006043083014</v>
       </c>
     </row>
     <row r="119" spans="1:5" x14ac:dyDescent="0.25">
@@ -3047,14 +3024,14 @@
         <v>47</v>
       </c>
       <c r="C119" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D119" t="s">
         <v>117</v>
       </c>
       <c r="E119" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C119,'Feed rations'!$V$5:$V$17,0),MATCH(B119,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>5.8607486129561623</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:5" x14ac:dyDescent="0.25">
@@ -3065,7 +3042,7 @@
         <v>47</v>
       </c>
       <c r="C120" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D120" t="s">
         <v>117</v>
@@ -3083,7 +3060,7 @@
         <v>47</v>
       </c>
       <c r="C121" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D121" t="s">
         <v>117</v>
@@ -3098,17 +3075,17 @@
         <v>42</v>
       </c>
       <c r="B122" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C122" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D122" t="s">
         <v>117</v>
       </c>
       <c r="E122" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C122,'Feed rations'!$V$5:$V$17,0),MATCH(B122,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>58.016195973989106</v>
+        <v>5.8607486129561623</v>
       </c>
     </row>
     <row r="123" spans="1:5" x14ac:dyDescent="0.25">
@@ -3116,10 +3093,10 @@
         <v>42</v>
       </c>
       <c r="B123" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C123" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D123" t="s">
         <v>117</v>
@@ -3134,17 +3111,17 @@
         <v>42</v>
       </c>
       <c r="B124" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="C124" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D124" t="s">
         <v>117</v>
       </c>
       <c r="E124" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C124,'Feed rations'!$V$5:$V$17,0),MATCH(B124,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>13.254201084237993</v>
+        <v>0</v>
       </c>
     </row>
     <row r="125" spans="1:5" x14ac:dyDescent="0.25">
@@ -3155,14 +3132,14 @@
         <v>48</v>
       </c>
       <c r="C125" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D125" t="s">
         <v>117</v>
       </c>
       <c r="E125" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C125,'Feed rations'!$V$5:$V$17,0),MATCH(B125,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>5.1156565588286975</v>
+        <v>58.016195973989106</v>
       </c>
     </row>
     <row r="126" spans="1:5" x14ac:dyDescent="0.25">
@@ -3173,14 +3150,14 @@
         <v>48</v>
       </c>
       <c r="C126" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D126" t="s">
         <v>117</v>
       </c>
       <c r="E126" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C126,'Feed rations'!$V$5:$V$17,0),MATCH(B126,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>8.2737362949343645</v>
+        <v>0</v>
       </c>
     </row>
     <row r="127" spans="1:5" x14ac:dyDescent="0.25">
@@ -3191,14 +3168,14 @@
         <v>48</v>
       </c>
       <c r="C127" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D127" t="s">
         <v>117</v>
       </c>
       <c r="E127" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C127,'Feed rations'!$V$5:$V$17,0),MATCH(B127,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>3.6907353080344469</v>
+        <v>13.254201084237993</v>
       </c>
     </row>
     <row r="128" spans="1:5" x14ac:dyDescent="0.25">
@@ -3209,14 +3186,14 @@
         <v>48</v>
       </c>
       <c r="C128" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D128" t="s">
         <v>117</v>
       </c>
       <c r="E128" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C128,'Feed rations'!$V$5:$V$17,0),MATCH(B128,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>5.1156565588286975</v>
       </c>
     </row>
     <row r="129" spans="1:5" x14ac:dyDescent="0.25">
@@ -3227,14 +3204,14 @@
         <v>48</v>
       </c>
       <c r="C129" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D129" t="s">
         <v>117</v>
       </c>
       <c r="E129" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C129,'Feed rations'!$V$5:$V$17,0),MATCH(B129,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3523367897362411</v>
+        <v>8.2737362949343645</v>
       </c>
     </row>
     <row r="130" spans="1:5" x14ac:dyDescent="0.25">
@@ -3245,14 +3222,14 @@
         <v>48</v>
       </c>
       <c r="C130" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D130" t="s">
         <v>117</v>
       </c>
       <c r="E130" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C130,'Feed rations'!$V$5:$V$17,0),MATCH(B130,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>1.5817437034433346</v>
+        <v>3.6907353080344469</v>
       </c>
     </row>
     <row r="131" spans="1:5" x14ac:dyDescent="0.25">
@@ -3263,7 +3240,7 @@
         <v>48</v>
       </c>
       <c r="C131" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D131" t="s">
         <v>117</v>
@@ -3281,14 +3258,14 @@
         <v>48</v>
       </c>
       <c r="C132" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D132" t="s">
         <v>117</v>
       </c>
       <c r="E132" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C132,'Feed rations'!$V$5:$V$17,0),MATCH(B132,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3523367897362411</v>
       </c>
     </row>
     <row r="133" spans="1:5" x14ac:dyDescent="0.25">
@@ -3299,14 +3276,14 @@
         <v>48</v>
       </c>
       <c r="C133" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D133" t="s">
         <v>117</v>
       </c>
       <c r="E133" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C133,'Feed rations'!$V$5:$V$17,0),MATCH(B133,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>6.1512255133907452</v>
+        <v>1.5817437034433346</v>
       </c>
     </row>
     <row r="134" spans="1:5" x14ac:dyDescent="0.25">
@@ -3317,14 +3294,14 @@
         <v>48</v>
       </c>
       <c r="C134" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D134" t="s">
         <v>117</v>
       </c>
       <c r="E134" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C134,'Feed rations'!$V$5:$V$17,0),MATCH(B134,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>1.5641687734050753</v>
+        <v>0</v>
       </c>
     </row>
     <row r="135" spans="1:5" x14ac:dyDescent="0.25">
@@ -3332,17 +3309,17 @@
         <v>42</v>
       </c>
       <c r="B135" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C135" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D135" t="s">
         <v>117</v>
       </c>
       <c r="E135" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C135,'Feed rations'!$V$5:$V$17,0),MATCH(B135,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.806020490924027</v>
+        <v>0</v>
       </c>
     </row>
     <row r="136" spans="1:5" x14ac:dyDescent="0.25">
@@ -3350,17 +3327,17 @@
         <v>42</v>
       </c>
       <c r="B136" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C136" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D136" t="s">
         <v>117</v>
       </c>
       <c r="E136" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C136,'Feed rations'!$V$5:$V$17,0),MATCH(B136,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>6.1512255133907452</v>
       </c>
     </row>
     <row r="137" spans="1:5" x14ac:dyDescent="0.25">
@@ -3368,17 +3345,17 @@
         <v>42</v>
       </c>
       <c r="B137" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="C137" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D137" t="s">
         <v>117</v>
       </c>
       <c r="E137" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C137,'Feed rations'!$V$5:$V$17,0),MATCH(B137,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>14.91384967080074</v>
+        <v>1.5641687734050753</v>
       </c>
     </row>
     <row r="138" spans="1:5" x14ac:dyDescent="0.25">
@@ -3389,14 +3366,14 @@
         <v>49</v>
       </c>
       <c r="C138" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D138" t="s">
         <v>117</v>
       </c>
       <c r="E138" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C138,'Feed rations'!$V$5:$V$17,0),MATCH(B138,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>8.3761840506164251</v>
+        <v>57.806020490924027</v>
       </c>
     </row>
     <row r="139" spans="1:5" x14ac:dyDescent="0.25">
@@ -3407,14 +3384,14 @@
         <v>49</v>
       </c>
       <c r="C139" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D139" t="s">
         <v>117</v>
       </c>
       <c r="E139" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C139,'Feed rations'!$V$5:$V$17,0),MATCH(B139,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.1368681474671822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="140" spans="1:5" x14ac:dyDescent="0.25">
@@ -3425,14 +3402,14 @@
         <v>49</v>
       </c>
       <c r="C140" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D140" t="s">
         <v>117</v>
       </c>
       <c r="E140" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C140,'Feed rations'!$V$5:$V$17,0),MATCH(B140,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.021954820011894</v>
+        <v>14.91384967080074</v>
       </c>
     </row>
     <row r="141" spans="1:5" x14ac:dyDescent="0.25">
@@ -3443,14 +3420,14 @@
         <v>49</v>
       </c>
       <c r="C141" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D141" t="s">
         <v>117</v>
       </c>
       <c r="E141" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C141,'Feed rations'!$V$5:$V$17,0),MATCH(B141,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>8.3761840506164251</v>
       </c>
     </row>
     <row r="142" spans="1:5" x14ac:dyDescent="0.25">
@@ -3461,14 +3438,14 @@
         <v>49</v>
       </c>
       <c r="C142" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D142" t="s">
         <v>117</v>
       </c>
       <c r="E142" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C142,'Feed rations'!$V$5:$V$17,0),MATCH(B142,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3652615404978614</v>
+        <v>4.1368681474671822</v>
       </c>
     </row>
     <row r="143" spans="1:5" x14ac:dyDescent="0.25">
@@ -3479,14 +3456,14 @@
         <v>49</v>
       </c>
       <c r="C143" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D143" t="s">
         <v>117</v>
       </c>
       <c r="E143" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C143,'Feed rations'!$V$5:$V$17,0),MATCH(B143,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0.7908718517216673</v>
+        <v>4.021954820011894</v>
       </c>
     </row>
     <row r="144" spans="1:5" x14ac:dyDescent="0.25">
@@ -3497,7 +3474,7 @@
         <v>49</v>
       </c>
       <c r="C144" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D144" t="s">
         <v>117</v>
@@ -3515,14 +3492,14 @@
         <v>49</v>
       </c>
       <c r="C145" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D145" t="s">
         <v>117</v>
       </c>
       <c r="E145" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C145,'Feed rations'!$V$5:$V$17,0),MATCH(B145,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3652615404978614</v>
       </c>
     </row>
     <row r="146" spans="1:5" x14ac:dyDescent="0.25">
@@ -3533,14 +3510,14 @@
         <v>49</v>
       </c>
       <c r="C146" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D146" t="s">
         <v>117</v>
       </c>
       <c r="E146" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C146,'Feed rations'!$V$5:$V$17,0),MATCH(B146,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>6.8069050412576626</v>
+        <v>0.7908718517216673</v>
       </c>
     </row>
     <row r="147" spans="1:5" x14ac:dyDescent="0.25">
@@ -3551,14 +3528,14 @@
         <v>49</v>
       </c>
       <c r="C147" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D147" t="s">
         <v>117</v>
       </c>
       <c r="E147" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C147,'Feed rations'!$V$5:$V$17,0),MATCH(B147,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0.78208438670253766</v>
+        <v>0</v>
       </c>
     </row>
     <row r="148" spans="1:5" x14ac:dyDescent="0.25">
@@ -3566,17 +3543,17 @@
         <v>42</v>
       </c>
       <c r="B148" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C148" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D148" t="s">
         <v>117</v>
       </c>
       <c r="E148" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C148,'Feed rations'!$V$5:$V$17,0),MATCH(B148,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.595845007858948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="149" spans="1:5" x14ac:dyDescent="0.25">
@@ -3584,17 +3561,17 @@
         <v>42</v>
       </c>
       <c r="B149" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C149" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D149" t="s">
         <v>117</v>
       </c>
       <c r="E149" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C149,'Feed rations'!$V$5:$V$17,0),MATCH(B149,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>6.8069050412576626</v>
       </c>
     </row>
     <row r="150" spans="1:5" x14ac:dyDescent="0.25">
@@ -3602,17 +3579,17 @@
         <v>42</v>
       </c>
       <c r="B150" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="C150" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D150" t="s">
         <v>117</v>
       </c>
       <c r="E150" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C150,'Feed rations'!$V$5:$V$17,0),MATCH(B150,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.573498257363489</v>
+        <v>0.78208438670253766</v>
       </c>
     </row>
     <row r="151" spans="1:5" x14ac:dyDescent="0.25">
@@ -3623,14 +3600,14 @@
         <v>50</v>
       </c>
       <c r="C151" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D151" t="s">
         <v>117</v>
       </c>
       <c r="E151" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C151,'Feed rations'!$V$5:$V$17,0),MATCH(B151,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>11.636711542404154</v>
+        <v>57.595845007858948</v>
       </c>
     </row>
     <row r="152" spans="1:5" x14ac:dyDescent="0.25">
@@ -3641,7 +3618,7 @@
         <v>50</v>
       </c>
       <c r="C152" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D152" t="s">
         <v>117</v>
@@ -3659,14 +3636,14 @@
         <v>50</v>
       </c>
       <c r="C153" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D153" t="s">
         <v>117</v>
       </c>
       <c r="E153" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C153,'Feed rations'!$V$5:$V$17,0),MATCH(B153,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.3531743319893401</v>
+        <v>16.573498257363489</v>
       </c>
     </row>
     <row r="154" spans="1:5" x14ac:dyDescent="0.25">
@@ -3677,14 +3654,14 @@
         <v>50</v>
       </c>
       <c r="C154" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D154" t="s">
         <v>117</v>
       </c>
       <c r="E154" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C154,'Feed rations'!$V$5:$V$17,0),MATCH(B154,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>11.636711542404154</v>
       </c>
     </row>
     <row r="155" spans="1:5" x14ac:dyDescent="0.25">
@@ -3695,14 +3672,14 @@
         <v>50</v>
       </c>
       <c r="C155" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D155" t="s">
         <v>117</v>
       </c>
       <c r="E155" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C155,'Feed rations'!$V$5:$V$17,0),MATCH(B155,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3781862912594818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="156" spans="1:5" x14ac:dyDescent="0.25">
@@ -3713,14 +3690,14 @@
         <v>50</v>
       </c>
       <c r="C156" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D156" t="s">
         <v>117</v>
       </c>
       <c r="E156" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C156,'Feed rations'!$V$5:$V$17,0),MATCH(B156,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>4.3531743319893401</v>
       </c>
     </row>
     <row r="157" spans="1:5" x14ac:dyDescent="0.25">
@@ -3731,7 +3708,7 @@
         <v>50</v>
       </c>
       <c r="C157" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D157" t="s">
         <v>117</v>
@@ -3749,14 +3726,14 @@
         <v>50</v>
       </c>
       <c r="C158" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D158" t="s">
         <v>117</v>
       </c>
       <c r="E158" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C158,'Feed rations'!$V$5:$V$17,0),MATCH(B158,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3781862912594818</v>
       </c>
     </row>
     <row r="159" spans="1:5" x14ac:dyDescent="0.25">
@@ -3767,14 +3744,14 @@
         <v>50</v>
       </c>
       <c r="C159" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D159" t="s">
         <v>117</v>
       </c>
       <c r="E159" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C159,'Feed rations'!$V$5:$V$17,0),MATCH(B159,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>7.4625845691245809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="160" spans="1:5" x14ac:dyDescent="0.25">
@@ -3785,7 +3762,7 @@
         <v>50</v>
       </c>
       <c r="C160" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D160" t="s">
         <v>117</v>
@@ -3800,17 +3777,17 @@
         <v>42</v>
       </c>
       <c r="B161" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C161" t="s">
-        <v>17</v>
+        <v>23</v>
       </c>
       <c r="D161" t="s">
         <v>117</v>
       </c>
       <c r="E161" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C161,'Feed rations'!$V$5:$V$17,0),MATCH(B161,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>57.595845007858948</v>
+        <v>0</v>
       </c>
     </row>
     <row r="162" spans="1:5" x14ac:dyDescent="0.25">
@@ -3818,17 +3795,17 @@
         <v>42</v>
       </c>
       <c r="B162" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C162" t="s">
-        <v>19</v>
+        <v>97</v>
       </c>
       <c r="D162" t="s">
         <v>117</v>
       </c>
       <c r="E162" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C162,'Feed rations'!$V$5:$V$17,0),MATCH(B162,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>7.4625845691245809</v>
       </c>
     </row>
     <row r="163" spans="1:5" x14ac:dyDescent="0.25">
@@ -3836,17 +3813,17 @@
         <v>42</v>
       </c>
       <c r="B163" t="s">
-        <v>94</v>
+        <v>50</v>
       </c>
       <c r="C163" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="D163" t="s">
         <v>117</v>
       </c>
       <c r="E163" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C163,'Feed rations'!$V$5:$V$17,0),MATCH(B163,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>16.573498257363489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="164" spans="1:5" x14ac:dyDescent="0.25">
@@ -3857,14 +3834,14 @@
         <v>94</v>
       </c>
       <c r="C164" t="s">
-        <v>64</v>
+        <v>17</v>
       </c>
       <c r="D164" t="s">
         <v>117</v>
       </c>
       <c r="E164" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C164,'Feed rations'!$V$5:$V$17,0),MATCH(B164,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>11.636711542404154</v>
+        <v>57.595845007858948</v>
       </c>
     </row>
     <row r="165" spans="1:5" x14ac:dyDescent="0.25">
@@ -3875,7 +3852,7 @@
         <v>94</v>
       </c>
       <c r="C165" t="s">
-        <v>87</v>
+        <v>19</v>
       </c>
       <c r="D165" t="s">
         <v>117</v>
@@ -3893,14 +3870,14 @@
         <v>94</v>
       </c>
       <c r="C166" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="D166" t="s">
         <v>117</v>
       </c>
       <c r="E166" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C166,'Feed rations'!$V$5:$V$17,0),MATCH(B166,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>4.3531743319893401</v>
+        <v>16.573498257363489</v>
       </c>
     </row>
     <row r="167" spans="1:5" x14ac:dyDescent="0.25">
@@ -3911,14 +3888,14 @@
         <v>94</v>
       </c>
       <c r="C167" t="s">
-        <v>21</v>
+        <v>64</v>
       </c>
       <c r="D167" t="s">
         <v>117</v>
       </c>
       <c r="E167" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C167,'Feed rations'!$V$5:$V$17,0),MATCH(B167,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>11.636711542404154</v>
       </c>
     </row>
     <row r="168" spans="1:5" x14ac:dyDescent="0.25">
@@ -3929,14 +3906,14 @@
         <v>94</v>
       </c>
       <c r="C168" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D168" t="s">
         <v>117</v>
       </c>
       <c r="E168" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C168,'Feed rations'!$V$5:$V$17,0),MATCH(B168,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>2.3781862912594818</v>
+        <v>0</v>
       </c>
     </row>
     <row r="169" spans="1:5" x14ac:dyDescent="0.25">
@@ -3947,14 +3924,14 @@
         <v>94</v>
       </c>
       <c r="C169" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="D169" t="s">
         <v>117</v>
       </c>
       <c r="E169" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C169,'Feed rations'!$V$5:$V$17,0),MATCH(B169,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>4.3531743319893401</v>
       </c>
     </row>
     <row r="170" spans="1:5" x14ac:dyDescent="0.25">
@@ -3965,7 +3942,7 @@
         <v>94</v>
       </c>
       <c r="C170" t="s">
-        <v>65</v>
+        <v>21</v>
       </c>
       <c r="D170" t="s">
         <v>117</v>
@@ -3983,14 +3960,14 @@
         <v>94</v>
       </c>
       <c r="C171" t="s">
-        <v>23</v>
+        <v>88</v>
       </c>
       <c r="D171" t="s">
         <v>117</v>
       </c>
       <c r="E171" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C171,'Feed rations'!$V$5:$V$17,0),MATCH(B171,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>0</v>
+        <v>2.3781862912594818</v>
       </c>
     </row>
     <row r="172" spans="1:5" x14ac:dyDescent="0.25">
@@ -4001,14 +3978,14 @@
         <v>94</v>
       </c>
       <c r="C172" t="s">
-        <v>97</v>
+        <v>22</v>
       </c>
       <c r="D172" t="s">
         <v>117</v>
       </c>
       <c r="E172" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C172,'Feed rations'!$V$5:$V$17,0),MATCH(B172,'Feed rations'!$AB$4:$AF$4,0))</f>
-        <v>7.4625845691245809</v>
+        <v>0</v>
       </c>
     </row>
     <row r="173" spans="1:5" x14ac:dyDescent="0.25">
@@ -4019,13 +3996,67 @@
         <v>94</v>
       </c>
       <c r="C173" t="s">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D173" t="s">
         <v>117</v>
       </c>
       <c r="E173" s="4">
         <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C173,'Feed rations'!$V$5:$V$17,0),MATCH(B173,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>42</v>
+      </c>
+      <c r="B174" t="s">
+        <v>94</v>
+      </c>
+      <c r="C174" t="s">
+        <v>23</v>
+      </c>
+      <c r="D174" t="s">
+        <v>117</v>
+      </c>
+      <c r="E174" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C174,'Feed rations'!$V$5:$V$17,0),MATCH(B174,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>42</v>
+      </c>
+      <c r="B175" t="s">
+        <v>94</v>
+      </c>
+      <c r="C175" t="s">
+        <v>97</v>
+      </c>
+      <c r="D175" t="s">
+        <v>117</v>
+      </c>
+      <c r="E175" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C175,'Feed rations'!$V$5:$V$17,0),MATCH(B175,'Feed rations'!$AB$4:$AF$4,0))</f>
+        <v>7.4625845691245809</v>
+      </c>
+    </row>
+    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A176" t="s">
+        <v>42</v>
+      </c>
+      <c r="B176" t="s">
+        <v>94</v>
+      </c>
+      <c r="C176" t="s">
+        <v>27</v>
+      </c>
+      <c r="D176" t="s">
+        <v>117</v>
+      </c>
+      <c r="E176" s="4">
+        <f>INDEX('Feed rations'!$AB$5:$AF$17,MATCH(C176,'Feed rations'!$V$5:$V$17,0),MATCH(B176,'Feed rations'!$AB$4:$AF$4,0))</f>
         <v>0</v>
       </c>
     </row>
